--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R58efb7e1dc9b47cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apply First" sheetId="2" r:id="R8c1aeada973b4d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Direct Jobs" sheetId="3" r:id="R91938a6f41e544f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Resume Matches" sheetId="4" r:id="Rec932ad118e746f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed Bad Links" sheetId="5" r:id="Rf22592f603994d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="6" r:id="Rf7a70bb558094fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R026985bd8dd94187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apply First" sheetId="2" r:id="Rbc741e9bfb1f4642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Direct Jobs" sheetId="3" r:id="Rf4ebd930204d49c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Resume Matches" sheetId="4" r:id="Rfdd051ba465a4cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed Bad Links" sheetId="5" r:id="R4cc386864f334d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="6" r:id="Rc2adffe70b574e76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,7 +57,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -114,6 +114,16 @@
         <x:fgColor rgb="FF6D28D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6D28D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -124,7 +134,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="114">
+  <x:cellXfs count="120">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
@@ -355,12 +365,22 @@
     <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0"/>
     <x:cellStyle name="Hyperlink" xfId="1"/>
   </x:cellStyles>
-  <x:dxfs count="40">
+  <x:dxfs count="66">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -377,7 +397,7 @@
         <x:color rgb="FF4B5563"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF3F4F6"/>
         </x:patternFill>
       </x:fill>
@@ -387,7 +407,7 @@
         <x:color rgb="FF1D4ED8"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDBEAFE"/>
         </x:patternFill>
       </x:fill>
@@ -397,7 +417,7 @@
         <x:color rgb="FF1E40AF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFBFDBFE"/>
         </x:patternFill>
       </x:fill>
@@ -407,7 +427,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -417,7 +437,7 @@
         <x:color rgb="FF78350F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -427,7 +447,7 @@
         <x:color rgb="FF3730A3"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0E7FF"/>
         </x:patternFill>
       </x:fill>
@@ -438,7 +458,7 @@
         <x:color rgb="FF5B21B6"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEDE9FE"/>
         </x:patternFill>
       </x:fill>
@@ -449,7 +469,7 @@
         <x:color rgb="FF4C1D95"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDD6FE"/>
         </x:patternFill>
       </x:fill>
@@ -460,7 +480,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -470,7 +490,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -480,7 +500,7 @@
         <x:color rgb="FF374151"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5E7EB"/>
         </x:patternFill>
       </x:fill>
@@ -490,7 +510,7 @@
         <x:color rgb="FF374151"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5E7EB"/>
         </x:patternFill>
       </x:fill>
@@ -500,7 +520,7 @@
         <x:color rgb="FF6B7280"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF3F4F6"/>
         </x:patternFill>
       </x:fill>
@@ -510,7 +530,7 @@
         <x:color rgb="FF4B5563"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF3F4F6"/>
         </x:patternFill>
       </x:fill>
@@ -520,7 +540,7 @@
         <x:color rgb="FF1D4ED8"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDBEAFE"/>
         </x:patternFill>
       </x:fill>
@@ -530,7 +550,7 @@
         <x:color rgb="FF1E40AF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFBFDBFE"/>
         </x:patternFill>
       </x:fill>
@@ -540,7 +560,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -550,7 +570,7 @@
         <x:color rgb="FF78350F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -560,7 +580,7 @@
         <x:color rgb="FF3730A3"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0E7FF"/>
         </x:patternFill>
       </x:fill>
@@ -571,7 +591,7 @@
         <x:color rgb="FF5B21B6"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEDE9FE"/>
         </x:patternFill>
       </x:fill>
@@ -582,7 +602,7 @@
         <x:color rgb="FF4C1D95"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDD6FE"/>
         </x:patternFill>
       </x:fill>
@@ -593,7 +613,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -603,7 +623,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -613,7 +633,7 @@
         <x:color rgb="FF374151"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5E7EB"/>
         </x:patternFill>
       </x:fill>
@@ -623,7 +643,7 @@
         <x:color rgb="FF374151"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5E7EB"/>
         </x:patternFill>
       </x:fill>
@@ -633,7 +653,7 @@
         <x:color rgb="FF6B7280"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF3F4F6"/>
         </x:patternFill>
       </x:fill>
@@ -643,7 +663,7 @@
         <x:color rgb="FF4B5563"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF3F4F6"/>
         </x:patternFill>
       </x:fill>
@@ -653,7 +673,7 @@
         <x:color rgb="FF1D4ED8"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDBEAFE"/>
         </x:patternFill>
       </x:fill>
@@ -663,7 +683,7 @@
         <x:color rgb="FF1E40AF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFBFDBFE"/>
         </x:patternFill>
       </x:fill>
@@ -673,7 +693,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -683,7 +703,7 @@
         <x:color rgb="FF78350F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -693,7 +713,7 @@
         <x:color rgb="FF3730A3"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0E7FF"/>
         </x:patternFill>
       </x:fill>
@@ -704,7 +724,7 @@
         <x:color rgb="FF5B21B6"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEDE9FE"/>
         </x:patternFill>
       </x:fill>
@@ -715,7 +735,7 @@
         <x:color rgb="FF4C1D95"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDD6FE"/>
         </x:patternFill>
       </x:fill>
@@ -726,7 +746,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -736,7 +756,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -746,7 +766,7 @@
         <x:color rgb="FF374151"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5E7EB"/>
         </x:patternFill>
       </x:fill>
@@ -756,7 +776,7 @@
         <x:color rgb="FF374151"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5E7EB"/>
         </x:patternFill>
       </x:fill>
@@ -766,7 +786,273 @@
         <x:color rgb="FF6B7280"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFF3F4F6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF4B5563"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF3F4F6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1D4ED8"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDBEAFE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1E40AF"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFBFDBFE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF78350F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFDE68A"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF3730A3"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE0E7FF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5B21B6"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFEDE9FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4C1D95"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDD6FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF991B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF374151"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5E7EB"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF374151"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5E7EB"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF6B7280"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF3F4F6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF4B5563"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF3F4F6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1D4ED8"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDBEAFE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1E40AF"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFBFDBFE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF78350F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFDE68A"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF3730A3"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE0E7FF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5B21B6"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFEDE9FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4C1D95"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDD6FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF991B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF374151"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5E7EB"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF374151"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5E7EB"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF6B7280"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFF3F4F6"/>
         </x:patternFill>
       </x:fill>
@@ -1714,16 +2000,16 @@
     <x:mergeCell ref="A12:J12"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R3c23505aad1549e6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R424fd9c2f43244f5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="Rb46a2df205b54fad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="R88a9359149384491"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="R7f2940eeef5c4e30"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="R846b8fd157eb426b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="R2631e3ad042248e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="R92fa9f98d9f04d1d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="Re82ec5985bd84c86"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="Re926a7f7faaf47c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R59bfb734f9a0488f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rabf1bbfd8c374321"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="R6c7dfbc5eb7440af"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="Rcaaeb8d836aa4f94"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="Rfb91904912444fcb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="R3c49eab84d3843d2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="R0300265aa8644bb9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="Rb0df01a9f6d64d18"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="Re904bc7fe7a0492c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="R6f44f375c8fd4364"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1748,6 +2034,8 @@
     <x:col min="13" max="13" width="14" customWidth="1"/>
     <x:col min="14" max="14" width="14" customWidth="1"/>
     <x:col min="15" max="15" width="28" customWidth="1"/>
+    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
@@ -1811,20 +2099,20 @@
           <x:t xml:space="preserve">Checked</x:t>
         </x:is>
       </x:c>
-      <x:c r="M1" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N1" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Date Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O1" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Notes</x:t>
-        </x:is>
+      <x:c r="M1" s="20" t="str">
+        <x:v>Status (linked)</x:v>
+      </x:c>
+      <x:c r="N1" s="20" t="str">
+        <x:v>Date Applied (linked)</x:v>
+      </x:c>
+      <x:c r="O1" s="20" t="str">
+        <x:v>Notes (linked)</x:v>
+      </x:c>
+      <x:c r="Q1" s="116" t="str">
+        <x:v>LIVE VIEW</x:v>
+      </x:c>
+      <x:c r="R1" s="116" t="str">
+        <x:v>Status, Date Applied, and Notes are linked from All Direct Jobs.</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1888,13 +2176,22 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M2" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N2" s="13" t="str"/>
-      <x:c r="O2" s="13" t="str"/>
+      <x:c r="M2" s="13" t="str">
+        <x:f>'All Direct Jobs'!M2</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N2" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N2="","",'All Direct Jobs'!N2)</x:f>
+      </x:c>
+      <x:c r="O2" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O2="","",'All Direct Jobs'!O2)</x:f>
+      </x:c>
+      <x:c r="Q2" s="79" t="str">
+        <x:v>Where to edit</x:v>
+      </x:c>
+      <x:c r="R2" s="79" t="str">
+        <x:v>Update those fields only in All Direct Jobs.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="inlineStr">
@@ -1957,13 +2254,22 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M3" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N3" s="13" t="str"/>
-      <x:c r="O3" s="13" t="str"/>
+      <x:c r="M3" s="13" t="str">
+        <x:f>'All Direct Jobs'!M3</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N3" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N3="","",'All Direct Jobs'!N3)</x:f>
+      </x:c>
+      <x:c r="O3" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O3="","",'All Direct Jobs'!O3)</x:f>
+      </x:c>
+      <x:c r="Q3" s="79" t="str">
+        <x:v>Why</x:v>
+      </x:c>
+      <x:c r="R3" s="79" t="str">
+        <x:v>One source of truth prevents conflicting application states.</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="13" t="inlineStr">
@@ -2026,13 +2332,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M4" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N4" s="13" t="str"/>
-      <x:c r="O4" s="13" t="str"/>
+      <x:c r="M4" s="13" t="str">
+        <x:f>'All Direct Jobs'!M4</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N4" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N4="","",'All Direct Jobs'!N4)</x:f>
+      </x:c>
+      <x:c r="O4" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O4="","",'All Direct Jobs'!O4)</x:f>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="inlineStr">
@@ -2095,13 +2404,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M5" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N5" s="13" t="str"/>
-      <x:c r="O5" s="13" t="str"/>
+      <x:c r="M5" s="13" t="str">
+        <x:f>'All Direct Jobs'!M5</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N5" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N5="","",'All Direct Jobs'!N5)</x:f>
+      </x:c>
+      <x:c r="O5" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O5="","",'All Direct Jobs'!O5)</x:f>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="inlineStr">
@@ -2164,13 +2476,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M6" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N6" s="13" t="str"/>
-      <x:c r="O6" s="13" t="str"/>
+      <x:c r="M6" s="13" t="str">
+        <x:f>'All Direct Jobs'!M6</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N6" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N6="","",'All Direct Jobs'!N6)</x:f>
+      </x:c>
+      <x:c r="O6" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O6="","",'All Direct Jobs'!O6)</x:f>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="inlineStr">
@@ -2233,13 +2548,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M7" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N7" s="13" t="str"/>
-      <x:c r="O7" s="13" t="str"/>
+      <x:c r="M7" s="13" t="str">
+        <x:f>'All Direct Jobs'!M8</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N7" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N8="","",'All Direct Jobs'!N8)</x:f>
+      </x:c>
+      <x:c r="O7" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O8="","",'All Direct Jobs'!O8)</x:f>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="13" t="inlineStr">
@@ -2302,13 +2620,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M8" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N8" s="13" t="str"/>
-      <x:c r="O8" s="13" t="str"/>
+      <x:c r="M8" s="13" t="str">
+        <x:f>'All Direct Jobs'!M9</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N8" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N9="","",'All Direct Jobs'!N9)</x:f>
+      </x:c>
+      <x:c r="O8" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O9="","",'All Direct Jobs'!O9)</x:f>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="13" t="inlineStr">
@@ -2371,13 +2692,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M9" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N9" s="13" t="str"/>
-      <x:c r="O9" s="13" t="str"/>
+      <x:c r="M9" s="13" t="str">
+        <x:f>'All Direct Jobs'!M10</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N9" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N10="","",'All Direct Jobs'!N10)</x:f>
+      </x:c>
+      <x:c r="O9" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O10="","",'All Direct Jobs'!O10)</x:f>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="13" t="inlineStr">
@@ -2440,13 +2764,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M10" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N10" s="13" t="str"/>
-      <x:c r="O10" s="13" t="str"/>
+      <x:c r="M10" s="13" t="str">
+        <x:f>'All Direct Jobs'!M11</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N10" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N11="","",'All Direct Jobs'!N11)</x:f>
+      </x:c>
+      <x:c r="O10" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O11="","",'All Direct Jobs'!O11)</x:f>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="13" t="inlineStr">
@@ -2509,13 +2836,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M11" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N11" s="13" t="str"/>
-      <x:c r="O11" s="13" t="str"/>
+      <x:c r="M11" s="13" t="str">
+        <x:f>'All Direct Jobs'!M13</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N11" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N13="","",'All Direct Jobs'!N13)</x:f>
+      </x:c>
+      <x:c r="O11" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O13="","",'All Direct Jobs'!O13)</x:f>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="13" t="inlineStr">
@@ -2578,13 +2908,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M12" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N12" s="13" t="str"/>
-      <x:c r="O12" s="13" t="str"/>
+      <x:c r="M12" s="13" t="str">
+        <x:f>'All Direct Jobs'!M29</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N12" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N29="","",'All Direct Jobs'!N29)</x:f>
+      </x:c>
+      <x:c r="O12" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O29="","",'All Direct Jobs'!O29)</x:f>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="13" t="inlineStr">
@@ -2647,13 +2980,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M13" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N13" s="13" t="str"/>
-      <x:c r="O13" s="13" t="str"/>
+      <x:c r="M13" s="13" t="str">
+        <x:f>'All Direct Jobs'!M32</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N13" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N32="","",'All Direct Jobs'!N32)</x:f>
+      </x:c>
+      <x:c r="O13" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O32="","",'All Direct Jobs'!O32)</x:f>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="13" t="inlineStr">
@@ -2716,13 +3052,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M14" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N14" s="13" t="str"/>
-      <x:c r="O14" s="13" t="str"/>
+      <x:c r="M14" s="13" t="str">
+        <x:f>'All Direct Jobs'!M33</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N14" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N33="","",'All Direct Jobs'!N33)</x:f>
+      </x:c>
+      <x:c r="O14" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O33="","",'All Direct Jobs'!O33)</x:f>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="13" t="inlineStr">
@@ -2785,13 +3124,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M15" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N15" s="13" t="str"/>
-      <x:c r="O15" s="13" t="str"/>
+      <x:c r="M15" s="13" t="str">
+        <x:f>'All Direct Jobs'!M36</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N15" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N36="","",'All Direct Jobs'!N36)</x:f>
+      </x:c>
+      <x:c r="O15" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O36="","",'All Direct Jobs'!O36)</x:f>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="13" t="inlineStr">
@@ -2854,13 +3196,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M16" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N16" s="13" t="str"/>
-      <x:c r="O16" s="13" t="str"/>
+      <x:c r="M16" s="13" t="str">
+        <x:f>'All Direct Jobs'!M37</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N16" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N37="","",'All Direct Jobs'!N37)</x:f>
+      </x:c>
+      <x:c r="O16" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O37="","",'All Direct Jobs'!O37)</x:f>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="13" t="inlineStr">
@@ -2923,13 +3268,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M17" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N17" s="13" t="str"/>
-      <x:c r="O17" s="13" t="str"/>
+      <x:c r="M17" s="13" t="str">
+        <x:f>'All Direct Jobs'!M38</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N17" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N38="","",'All Direct Jobs'!N38)</x:f>
+      </x:c>
+      <x:c r="O17" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O38="","",'All Direct Jobs'!O38)</x:f>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="13" t="inlineStr">
@@ -2992,13 +3340,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M18" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N18" s="13" t="str"/>
-      <x:c r="O18" s="13" t="str"/>
+      <x:c r="M18" s="13" t="str">
+        <x:f>'All Direct Jobs'!M39</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N18" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N39="","",'All Direct Jobs'!N39)</x:f>
+      </x:c>
+      <x:c r="O18" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O39="","",'All Direct Jobs'!O39)</x:f>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="13" t="inlineStr">
@@ -3061,13 +3412,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M19" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N19" s="13" t="str"/>
-      <x:c r="O19" s="13" t="str"/>
+      <x:c r="M19" s="13" t="str">
+        <x:f>'All Direct Jobs'!M40</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N19" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N40="","",'All Direct Jobs'!N40)</x:f>
+      </x:c>
+      <x:c r="O19" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O40="","",'All Direct Jobs'!O40)</x:f>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="13" t="inlineStr">
@@ -3130,13 +3484,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M20" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N20" s="13" t="str"/>
-      <x:c r="O20" s="13" t="str"/>
+      <x:c r="M20" s="13" t="str">
+        <x:f>'All Direct Jobs'!M41</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N20" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N41="","",'All Direct Jobs'!N41)</x:f>
+      </x:c>
+      <x:c r="O20" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O41="","",'All Direct Jobs'!O41)</x:f>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="13" t="inlineStr">
@@ -3199,13 +3556,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M21" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N21" s="13" t="str"/>
-      <x:c r="O21" s="13" t="str"/>
+      <x:c r="M21" s="13" t="str">
+        <x:f>'All Direct Jobs'!M43</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N21" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N43="","",'All Direct Jobs'!N43)</x:f>
+      </x:c>
+      <x:c r="O21" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O43="","",'All Direct Jobs'!O43)</x:f>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="13" t="inlineStr">
@@ -3268,13 +3628,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M22" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N22" s="13" t="str"/>
-      <x:c r="O22" s="13" t="str"/>
+      <x:c r="M22" s="13" t="str">
+        <x:f>'All Direct Jobs'!M46</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N22" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N46="","",'All Direct Jobs'!N46)</x:f>
+      </x:c>
+      <x:c r="O22" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O46="","",'All Direct Jobs'!O46)</x:f>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="13" t="inlineStr">
@@ -3337,13 +3700,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M23" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N23" s="13" t="str"/>
-      <x:c r="O23" s="13" t="str"/>
+      <x:c r="M23" s="13" t="str">
+        <x:f>'All Direct Jobs'!M48</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N23" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N48="","",'All Direct Jobs'!N48)</x:f>
+      </x:c>
+      <x:c r="O23" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O48="","",'All Direct Jobs'!O48)</x:f>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="13" t="inlineStr">
@@ -3406,13 +3772,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M24" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N24" s="13" t="str"/>
-      <x:c r="O24" s="13" t="str"/>
+      <x:c r="M24" s="13" t="str">
+        <x:f>'All Direct Jobs'!M52</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N24" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N52="","",'All Direct Jobs'!N52)</x:f>
+      </x:c>
+      <x:c r="O24" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O52="","",'All Direct Jobs'!O52)</x:f>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="13" t="inlineStr">
@@ -3475,13 +3844,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M25" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N25" s="13" t="str"/>
-      <x:c r="O25" s="13" t="str"/>
+      <x:c r="M25" s="13" t="str">
+        <x:f>'All Direct Jobs'!M55</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N25" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N55="","",'All Direct Jobs'!N55)</x:f>
+      </x:c>
+      <x:c r="O25" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O55="","",'All Direct Jobs'!O55)</x:f>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="13" t="inlineStr">
@@ -3544,13 +3916,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M26" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N26" s="13" t="str"/>
-      <x:c r="O26" s="13" t="str"/>
+      <x:c r="M26" s="13" t="str">
+        <x:f>'All Direct Jobs'!M61</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N26" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N61="","",'All Direct Jobs'!N61)</x:f>
+      </x:c>
+      <x:c r="O26" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O61="","",'All Direct Jobs'!O61)</x:f>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="13" t="inlineStr">
@@ -3613,13 +3988,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M27" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N27" s="13" t="str"/>
-      <x:c r="O27" s="13" t="str"/>
+      <x:c r="M27" s="13" t="str">
+        <x:f>'All Direct Jobs'!M62</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N27" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N62="","",'All Direct Jobs'!N62)</x:f>
+      </x:c>
+      <x:c r="O27" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O62="","",'All Direct Jobs'!O62)</x:f>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="13" t="inlineStr">
@@ -3682,13 +4060,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M28" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N28" s="13" t="str"/>
-      <x:c r="O28" s="13" t="str"/>
+      <x:c r="M28" s="13" t="str">
+        <x:f>'All Direct Jobs'!M63</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N28" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N63="","",'All Direct Jobs'!N63)</x:f>
+      </x:c>
+      <x:c r="O28" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O63="","",'All Direct Jobs'!O63)</x:f>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="13" t="inlineStr">
@@ -3751,13 +4132,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M29" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N29" s="13" t="str"/>
-      <x:c r="O29" s="13" t="str"/>
+      <x:c r="M29" s="13" t="str">
+        <x:f>'All Direct Jobs'!M64</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N29" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N64="","",'All Direct Jobs'!N64)</x:f>
+      </x:c>
+      <x:c r="O29" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O64="","",'All Direct Jobs'!O64)</x:f>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="13" t="inlineStr">
@@ -3820,124 +4204,122 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M30" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N30" s="13" t="str"/>
-      <x:c r="O30" s="13" t="str"/>
+      <x:c r="M30" s="13" t="str">
+        <x:f>'All Direct Jobs'!M65</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N30" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N65="","",'All Direct Jobs'!N65)</x:f>
+      </x:c>
+      <x:c r="O30" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O65="","",'All Direct Jobs'!O65)</x:f>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="M2:M100">
-    <x:cfRule type="expression" dxfId="1" priority="1">
+    <x:cfRule type="expression" dxfId="40" priority="1">
       <x:formula>M2="Not Applied"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="2" priority="2">
+    <x:cfRule type="expression" dxfId="41" priority="2">
       <x:formula>M2="Planning to Apply"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="3" priority="3">
+    <x:cfRule type="expression" dxfId="42" priority="3">
       <x:formula>M2="Applied"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="4" priority="4">
+    <x:cfRule type="expression" dxfId="43" priority="4">
       <x:formula>M2="Under Consideration"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="5" priority="5">
+    <x:cfRule type="expression" dxfId="44" priority="5">
       <x:formula>M2="OA / Assessment"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="6" priority="6">
+    <x:cfRule type="expression" dxfId="45" priority="6">
       <x:formula>M2="Recruiter Screen"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="7" priority="7">
+    <x:cfRule type="expression" dxfId="46" priority="7">
       <x:formula>M2="Interview"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="8" priority="8">
+    <x:cfRule type="expression" dxfId="47" priority="8">
       <x:formula>M2="Final Round"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="9" priority="9">
+    <x:cfRule type="expression" dxfId="48" priority="9">
       <x:formula>M2="Offer"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="10" priority="10">
+    <x:cfRule type="expression" dxfId="49" priority="10">
       <x:formula>M2="Rejected"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="11" priority="11">
+    <x:cfRule type="expression" dxfId="50" priority="11">
       <x:formula>M2="Withdrawn"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="12" priority="12">
+    <x:cfRule type="expression" dxfId="51" priority="12">
       <x:formula>M2="Not Going to Apply"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="13" priority="13">
+    <x:cfRule type="expression" dxfId="52" priority="13">
       <x:formula>M2="Closed / Expired"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="M2:M100">
-      <x:formula1>"Not Applied,Planning to Apply,Applied,Under Consideration,OA / Assessment,Recruiter Screen,Interview,Final Round,Offer,Rejected,Withdrawn,Not Going to Apply,Closed / Expired"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="Rf7d091359e1648f0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="Rbd3c59f27025440e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="Ra1b4b00cbb3440e1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="R5cc5755d3a2a4dcb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="R1ad5f708e1234e72"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R9b265ba808e046a7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="R1ef8a40b9c904778"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="Rbfa738df7c594b49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="R17c6f5faff2a40bc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="Rcd80206d1e514237"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="R8f1b99b328f14b5b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="Rf1106201ba27462f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="R15c72fcfdc584a6c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="Rd876035bed2a4c45"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="Rfd0538d3ed8f43d4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R27de0446ba3f45c3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R32e44187be22451d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R1cdfb659c1eb4d6d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="Raa994daef855443d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="Rc981f16c173c4007"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="Re9690c3129634e68"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="Raf297f2e0f6d4703"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="Ra3f0178810b14853"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rc5f9523713104a09"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="R715738b312cc413e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R4fd4c61b31824081"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="Rab19bc6b309c4ddf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R6d48b2bae3dc43b0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="Rf38dc5c4fb164819"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Rd27772ee5b914e45"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R15ae152a21594b99"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="R8166c9c6945d45cd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="Rcb2dd36c8e1a48a3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="R1d4431c30c0c404d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="R29c47a64cabd4be3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Rcd77a2a99d124473"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="R658c28a05b474ee2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R355d14d5db274231"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="R27399b71a4844acd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="R21f70205c0c347ec"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="R0dd98c90c2f74736"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="R7841535d51f74420"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="Rebbeab0920ba488f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R2b9d017215c847a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="R73bb43bd328c49d6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="Rc265837f5fbe4789"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R81a0178f91204392"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R31cc72d715c84acc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="Rca746592960b48f4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R97afa4affcb149e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="Rc359313debdc4f93"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="R9a61fbe3133743b4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="Rceb6ba052ef94552"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Rb3c66e932814411f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="R5b4791d838654844"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="Rf77f8125b9ca460f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="R0a692e3e95f74c0c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="R87d10cde8e334785"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="Rf11ed172cb234a62"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="R1976dea6ae524bc0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="R95c5aba4a5fa4624"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="Re6a21d82f6d54b4d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="Rf3548787e6c94571"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R30b153f71b744431"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="Rd91d2bf057574fb1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R1969d0b64426472a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="Rbde4f981383c4abc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R56373c85cef640dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="R20771940001a43b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R3455bb69d6654bc0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="Rcfd098aa756b4279"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R2519de53429943e9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="R102d5bd834994c64"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Rd9da1255d74c498f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="Rdbd3a3892ea949a1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Rd5c532dba11a41f6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="R8f8ce0426be04216"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R20f4169d953f4a4e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="R08824226af45451f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R0829e9e7aaa8451f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="R4139528fb1d0464c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rd4d8f2de19b044a5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="R7ce4d44b5be2453a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R9f539a0b312f43ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="R9cabdcfd805c4759"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R04f7ee78383b40ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="R96ec93fbdf704eb0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Rcbdc0f6fd4184633"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R45368bae3f4f4dcf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="Rb194152c68864fc6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="R5ffd752740e546c4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="R695928567e654662"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="Rea008057a21041bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R977f911e73c5487c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Re155f46d6ba44203"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Ra16981647e274dc4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="R5e459e69033f4587"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="Rc34f6062146c43e6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="R22744c3e91244d6b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rb9a7144408644aa8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="R384899433f9a4ae3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Re200e7a4e95a49ed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="Rf3b3519d7ac94dce"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R0fedf8e6eb7f4b23"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="Ra7e15976d51642a8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R0e9fd8fda13042e0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="R9448259e7af94f92"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="Rf7e7b3c981564ffd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="R6ab24d88c32c46ae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="R301ae46f98754d30"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="R96bfff9299f6459c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R969c6b06c50149cb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="R3d042d837bce4cea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="R48b3bd59f18841b8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="R9b2f7d7cd85b44e0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="R19143322d6784384"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R493c6f30412545b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c80016a0bc14b84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8647,142 +9029,142 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="Rd0c7308099914896"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="R8f17e6462cb74fdf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="R2eda45e0f067445c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="Rcb101f1ad1f846e9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="R60300af0d30d434c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="Rd1c876c9d91c46a7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="Rcfd8f5cb364640eb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R19b92d01af574bbc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="R817fcb64805c4a78"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R8802dac0a28745fb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="R295313fcff8d429f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R293ef9755572467e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="R65a982fa54f3466e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R5ddf5b1ab01e43b2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="R08b5d26643144248"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R5a9bfb17eca64e59"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R566e8711d89e4450"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R358458b5753445b6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="R9a3bf286e22c4044"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R6e72e2e6678145cc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="Rb4d3190561114a69"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R5ef4ec139b9b4a70"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="R6bc0d34bb0b44530"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R78e8c0d51da947a1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="R5094e132dd424b1b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R49f991a032f24331"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="R5cffd98811024cbf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R5c45d5e4644f464e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="R19803d269977453a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Rb4f86bf2315c4299"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="Rb1dad057d48f4705"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="Rea0de83bd47840cc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="R616e869ecddb40bb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="Rb1fc397da919417c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="R8fcd7b64aac7462e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R56fbec0b6198458b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="R7c2eb56f506147da"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rf4e394864bfc421c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="R916ae9422c9d44a1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="R24d9320876304b13"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="Rcddfadd8bce34b60"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="R0631bd7e82384bbe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="R08494898b00a4d11"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R7b9d4c04eaf645b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="R5b9a4ed1fe594bef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="Rec7c6057f4c34e0e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R00b57f7757b34d76"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R9d64624382ea43e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="Rdf6bd21196264ac1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R0f5a960676f04f94"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="Rc15b06b490bf4868"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="R39474558b09e444d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="Rc0af8491ded5452a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R83da38b499334790"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="Rcbf0b1d087124fd3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="R0aeb159f07eb42bb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="R2c0c3bdf95124b47"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="R8db210c6cf144d31"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="Rf8e9ef9d87cf4e53"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R6dc2cd2210274167"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="R4d8f965b9ba14f4e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="R233ded6debf24b12"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="Rb26b58428b4e4f04"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="Rdd1e6a4753c045ed"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="R2871a0aa70a741b3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R4512b151d0f14148"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="R22196d0bd57948a6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="Ra7a51d7cfe924fc2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="Rad09e82c05db49de"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Re3bc1dfb80964298"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="R498302a995fe4d09"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="R151570ccec154f0c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="Rf519400cc34345cf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R2f97b67670694082"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="Ra5e8b8d16b4446c4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="Re2e0a00b4bb94fa0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="R914e9bc58d414e25"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="Rc72eceb5ee254dc2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="R658ff33f1f844378"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="Rbe150600e13d41ff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="Ra84c2ff8b7b84973"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="R82839d9c9e514aaf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="R46800a75fb054642"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="R127975e59ad54732"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="R33fd5c423b084d78"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="R23b98f10b28543e7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="R9c7ee8e4bf5047a1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="R904b3d587e464ed8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="Rc74e1586057b4ed3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="Rcd931eb57cbc4b0b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="R9e97270ae49a41a5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="R8ca47476558c4b85"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="Rebb82eb3ca324341"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="R5decf816d832498a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="R8758baed8b094600"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="R38e73297ee82432e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="Rdb5f025fc9ec4ad8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="Rd9875134824347f6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="R9fe675d5e9fc4f10"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="R0b4bb773016c4c34"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="Rcf91b54a9d76444c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="R3a56264540af49a9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="R306612d080c745ac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="R50ef13ad009c44a4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="Rf89da5d731b14495"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="R3e28a919ceb141ac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="R40906bdd55e248c2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="R09c36b51deba48f3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="R78361f1df0cd4fbd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="Ra3070cc298304b92"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="Rbf51e971926c45e6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="R33e81d36ce264dea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="R8b49d95d66504fb3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="R39e03deccefe45b7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="R2b883aa267c44ebf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="R293b9755216f4cf4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="R6be31e88e5ea4d49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="R087afa6480e74139"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="R367c2fe8e3734930"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="R1696111a433e4857"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="Rd73720f9290046a4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="Rb7fe51d9d04d4c39"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="R2cc245f6e4e44933"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="Ra22b7aeecb9a439d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R994c1af2a67a49e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="Rcbf9fd2f4db04d3c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="Re1ddad25ad614a0b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="R9ae8fe8479e74521"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="Rac331cd4dbf5426f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="Rbfb24d1564064811"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="R7ed722fad0a34f75"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="R3eb52e99043f4d77"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="R0f2c4a7ac66243c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="Rb8fc2c42a1cc40ae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="R5a0d3ca294b149ab"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="R81f797c21aea44c7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="R47b2ecf9fd674d52"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="Rd1a66ecacf0f4062"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="Rf530d5eb43ff4ddb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R5e16531d5f0c4640"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="R6550092e98ed43ad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R19d7a06920ad4e4d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="Raed7c6402674475c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R0126ca856c764b82"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="Rcb5cf26940304fbb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="Rbda7ead1e0e249c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="Refcc38bc822c4c11"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R2749af6e0ec54a0a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="Ra6c2a12a3a9b41f6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R408a630be8c644d3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="R070bb4ba861a4d55"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R27e846441aaf4f8c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="Refa63dd6adce4a71"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R2d89b38cc9f24a23"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="R55fc94891b1c43cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R517863078fd54ed1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="R87e0c930f2004a41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rdadc99336bbf4463"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="Rb8d90c4c5d4d4fd5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R7eef8d3bd8bf48d9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="Re14852f4b5f949cc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R93ee54c9c8364849"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="Rfd0a3d4056274511"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="R26dcbba4a0844da0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="Rdc0ac090e73f4022"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="R2a375031c5324603"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="Rfb47aa358f964e2a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R377bf45609f1461e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Rc2caeb02eb544295"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R528a38bb2d344071"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="Rc04d6e7bbb4b4abf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="Raa84cad2351d4dd0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="Rf796a9e50d67452e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rebfecade0bfc4e57"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="Rc0f6183a981a42ff"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Rf5667ce4a42f450d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="Rf6e626a1de4c4c3a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R79dc5ef221f44e11"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R9a2992b45e704da5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R8dd878d626114884"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="R03012ff32d7e44b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="Rebfdcd1f22544b73"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="R957ae90cfbf64f87"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="R85b8262fd6024f95"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="R915df1ea102e4c70"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Rca02640835d94029"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="Re06cc03dd8d34f64"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="Rf5bc5aa88e7e4d47"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="R1903590f593343a4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="R2395f1d38a1f4de1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="R85413c2b3dc8453d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R3630ccfe16eb491f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="Rb6304b0660c843b7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="R615c1b6fdd464c08"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="R79d6c150a5ee494c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="Rc6dbbac7fe8e4c1c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="R0abcaad56355489c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="Rc86fe76a85d94564"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="Rb3a5b6f3859a4169"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R6d24823cd17141ac"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="R0cd737c319324960"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rae396d204b1e4054"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="Ra506ca4ea77f4097"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="R6606fe315f904337"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="R7fe8ec638b5d41ed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R89e4e8cc1f2d4105"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="Rcfdf5cef95df4345"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="Ra6e87408d5f0445e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="R5a9cf868254d4b07"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R365cdf4533d34997"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="Rab0cdac841144484"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="R140d632b7fa241b6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="R6b1a1187fdfb4fa1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="R71c79db7f80a45f0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="R347f4b669e9042d5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="Rea20f82add2b448e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="Rd3bb3a9682934ac2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="R11a977cb145e4881"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="R2b3346475b6942ca"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="Rf40dd7c4c7954187"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="R048479f32a1d4938"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="R16ef085308f146b0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="R607a228e810f4790"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="R2f8a98f18106470d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="R185c12de2a194e79"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="Rdab21de734d148ae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="R1d23788c109649b0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="R7a31e1c268bd440f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="Reeb4038726d342a7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="R8c6bc953cf264f3a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="R5e44a87faeda4e25"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="R60af49bc4d064373"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="Rd7f17056888b4f35"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="R699c2e9ea38f4e38"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="R863d5aa6d4394133"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="Rc46f89f6f7564b34"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="Rbf87587b925d46ea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="Reecdcf3b0f6b4eb5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="R9f943be6b4f84b2d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="Rb82fe17ad9454984"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="Rfcd2a958dbf1427b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="R0151ea2f8a68431c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="R0eb5c54bcb54476d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="R6ad3a0346b024706"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="R2f11b0a900be4364"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="Rf3ac6248809847cb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="R59811527d4e24209"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="Rde63dc37c3f34431"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="Rb2dd206fecab4b6a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="Rb92d23a02dec4390"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="Reab56d00db594e4c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="R691638291a954f93"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="Re5e17051c23543dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="R4edd57915eab44af"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="R57c94d3c09b8451a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="R0b8cb5882d324317"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R558132c4412d42ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="R0136bda394a24d34"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="R2c07c4493dc5407f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="Rf2f69b54613f4921"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="Red410fd2698b42a4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="R8ce0f3c40e3b452d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="R07f1d31486124879"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="R012febda0a5e450a"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc0503ba391e4b63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a98899604764427"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8806,6 +9188,8 @@
     <x:col min="13" max="13" width="14" customWidth="1"/>
     <x:col min="14" max="14" width="14" customWidth="1"/>
     <x:col min="15" max="15" width="28" customWidth="1"/>
+    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
@@ -8869,20 +9253,20 @@
           <x:t xml:space="preserve">Checked</x:t>
         </x:is>
       </x:c>
-      <x:c r="M1" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N1" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Date Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O1" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Notes</x:t>
-        </x:is>
+      <x:c r="M1" s="29" t="str">
+        <x:v>Status (linked)</x:v>
+      </x:c>
+      <x:c r="N1" s="29" t="str">
+        <x:v>Date Applied (linked)</x:v>
+      </x:c>
+      <x:c r="O1" s="29" t="str">
+        <x:v>Notes (linked)</x:v>
+      </x:c>
+      <x:c r="Q1" s="116" t="str">
+        <x:v>LIVE VIEW</x:v>
+      </x:c>
+      <x:c r="R1" s="116" t="str">
+        <x:v>Status, Date Applied, and Notes are linked from All Direct Jobs.</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -8946,13 +9330,22 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M2" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N2" s="13" t="str"/>
-      <x:c r="O2" s="13" t="str"/>
+      <x:c r="M2" s="13" t="str">
+        <x:f>'All Direct Jobs'!M2</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N2" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N2="","",'All Direct Jobs'!N2)</x:f>
+      </x:c>
+      <x:c r="O2" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O2="","",'All Direct Jobs'!O2)</x:f>
+      </x:c>
+      <x:c r="Q2" s="79" t="str">
+        <x:v>Where to edit</x:v>
+      </x:c>
+      <x:c r="R2" s="79" t="str">
+        <x:v>Update those fields only in All Direct Jobs.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="inlineStr">
@@ -9015,13 +9408,22 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M3" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N3" s="13" t="str"/>
-      <x:c r="O3" s="13" t="str"/>
+      <x:c r="M3" s="13" t="str">
+        <x:f>'All Direct Jobs'!M5</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N3" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N5="","",'All Direct Jobs'!N5)</x:f>
+      </x:c>
+      <x:c r="O3" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O5="","",'All Direct Jobs'!O5)</x:f>
+      </x:c>
+      <x:c r="Q3" s="79" t="str">
+        <x:v>Why</x:v>
+      </x:c>
+      <x:c r="R3" s="79" t="str">
+        <x:v>One source of truth prevents conflicting application states.</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="13" t="inlineStr">
@@ -9084,13 +9486,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M4" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N4" s="13" t="str"/>
-      <x:c r="O4" s="13" t="str"/>
+      <x:c r="M4" s="13" t="str">
+        <x:f>'All Direct Jobs'!M6</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N4" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N6="","",'All Direct Jobs'!N6)</x:f>
+      </x:c>
+      <x:c r="O4" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O6="","",'All Direct Jobs'!O6)</x:f>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="inlineStr">
@@ -9153,13 +9558,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M5" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N5" s="13" t="str"/>
-      <x:c r="O5" s="13" t="str"/>
+      <x:c r="M5" s="13" t="str">
+        <x:f>'All Direct Jobs'!M8</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N5" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N8="","",'All Direct Jobs'!N8)</x:f>
+      </x:c>
+      <x:c r="O5" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O8="","",'All Direct Jobs'!O8)</x:f>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="inlineStr">
@@ -9222,13 +9630,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M6" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N6" s="13" t="str"/>
-      <x:c r="O6" s="13" t="str"/>
+      <x:c r="M6" s="13" t="str">
+        <x:f>'All Direct Jobs'!M9</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N6" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N9="","",'All Direct Jobs'!N9)</x:f>
+      </x:c>
+      <x:c r="O6" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O9="","",'All Direct Jobs'!O9)</x:f>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="inlineStr">
@@ -9291,13 +9702,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M7" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N7" s="13" t="str"/>
-      <x:c r="O7" s="13" t="str"/>
+      <x:c r="M7" s="13" t="str">
+        <x:f>'All Direct Jobs'!M10</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N7" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N10="","",'All Direct Jobs'!N10)</x:f>
+      </x:c>
+      <x:c r="O7" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O10="","",'All Direct Jobs'!O10)</x:f>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="13" t="inlineStr">
@@ -9360,13 +9774,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M8" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N8" s="13" t="str"/>
-      <x:c r="O8" s="13" t="str"/>
+      <x:c r="M8" s="13" t="str">
+        <x:f>'All Direct Jobs'!M11</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N8" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N11="","",'All Direct Jobs'!N11)</x:f>
+      </x:c>
+      <x:c r="O8" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O11="","",'All Direct Jobs'!O11)</x:f>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="13" t="inlineStr">
@@ -9429,13 +9846,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M9" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N9" s="13" t="str"/>
-      <x:c r="O9" s="13" t="str"/>
+      <x:c r="M9" s="13" t="str">
+        <x:f>'All Direct Jobs'!M12</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N9" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N12="","",'All Direct Jobs'!N12)</x:f>
+      </x:c>
+      <x:c r="O9" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O12="","",'All Direct Jobs'!O12)</x:f>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="13" t="inlineStr">
@@ -9498,13 +9918,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M10" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N10" s="13" t="str"/>
-      <x:c r="O10" s="13" t="str"/>
+      <x:c r="M10" s="13" t="str">
+        <x:f>'All Direct Jobs'!M13</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N10" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N13="","",'All Direct Jobs'!N13)</x:f>
+      </x:c>
+      <x:c r="O10" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O13="","",'All Direct Jobs'!O13)</x:f>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="13" t="inlineStr">
@@ -9567,13 +9990,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M11" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N11" s="13" t="str"/>
-      <x:c r="O11" s="13" t="str"/>
+      <x:c r="M11" s="13" t="str">
+        <x:f>'All Direct Jobs'!M14</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N11" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N14="","",'All Direct Jobs'!N14)</x:f>
+      </x:c>
+      <x:c r="O11" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O14="","",'All Direct Jobs'!O14)</x:f>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="13" t="inlineStr">
@@ -9636,13 +10062,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M12" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N12" s="13" t="str"/>
-      <x:c r="O12" s="13" t="str"/>
+      <x:c r="M12" s="13" t="str">
+        <x:f>'All Direct Jobs'!M16</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N12" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N16="","",'All Direct Jobs'!N16)</x:f>
+      </x:c>
+      <x:c r="O12" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O16="","",'All Direct Jobs'!O16)</x:f>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="13" t="inlineStr">
@@ -9705,13 +10134,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M13" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N13" s="13" t="str"/>
-      <x:c r="O13" s="13" t="str"/>
+      <x:c r="M13" s="13" t="str">
+        <x:f>'All Direct Jobs'!M17</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N13" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N17="","",'All Direct Jobs'!N17)</x:f>
+      </x:c>
+      <x:c r="O13" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O17="","",'All Direct Jobs'!O17)</x:f>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="13" t="inlineStr">
@@ -9774,13 +10206,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M14" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N14" s="13" t="str"/>
-      <x:c r="O14" s="13" t="str"/>
+      <x:c r="M14" s="13" t="str">
+        <x:f>'All Direct Jobs'!M20</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N14" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N20="","",'All Direct Jobs'!N20)</x:f>
+      </x:c>
+      <x:c r="O14" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O20="","",'All Direct Jobs'!O20)</x:f>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="13" t="inlineStr">
@@ -9843,13 +10278,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M15" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N15" s="13" t="str"/>
-      <x:c r="O15" s="13" t="str"/>
+      <x:c r="M15" s="13" t="str">
+        <x:f>'All Direct Jobs'!M22</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N15" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N22="","",'All Direct Jobs'!N22)</x:f>
+      </x:c>
+      <x:c r="O15" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O22="","",'All Direct Jobs'!O22)</x:f>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="13" t="inlineStr">
@@ -9912,13 +10350,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M16" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N16" s="13" t="str"/>
-      <x:c r="O16" s="13" t="str"/>
+      <x:c r="M16" s="13" t="str">
+        <x:f>'All Direct Jobs'!M23</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N16" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N23="","",'All Direct Jobs'!N23)</x:f>
+      </x:c>
+      <x:c r="O16" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O23="","",'All Direct Jobs'!O23)</x:f>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="13" t="inlineStr">
@@ -9981,13 +10422,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M17" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N17" s="13" t="str"/>
-      <x:c r="O17" s="13" t="str"/>
+      <x:c r="M17" s="13" t="str">
+        <x:f>'All Direct Jobs'!M24</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N17" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N24="","",'All Direct Jobs'!N24)</x:f>
+      </x:c>
+      <x:c r="O17" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O24="","",'All Direct Jobs'!O24)</x:f>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="13" t="inlineStr">
@@ -10050,13 +10494,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M18" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N18" s="13" t="str"/>
-      <x:c r="O18" s="13" t="str"/>
+      <x:c r="M18" s="13" t="str">
+        <x:f>'All Direct Jobs'!M26</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N18" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N26="","",'All Direct Jobs'!N26)</x:f>
+      </x:c>
+      <x:c r="O18" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O26="","",'All Direct Jobs'!O26)</x:f>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="13" t="inlineStr">
@@ -10119,13 +10566,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M19" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N19" s="13" t="str"/>
-      <x:c r="O19" s="13" t="str"/>
+      <x:c r="M19" s="13" t="str">
+        <x:f>'All Direct Jobs'!M27</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N19" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N27="","",'All Direct Jobs'!N27)</x:f>
+      </x:c>
+      <x:c r="O19" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O27="","",'All Direct Jobs'!O27)</x:f>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="13" t="inlineStr">
@@ -10188,13 +10638,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M20" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N20" s="13" t="str"/>
-      <x:c r="O20" s="13" t="str"/>
+      <x:c r="M20" s="13" t="str">
+        <x:f>'All Direct Jobs'!M36</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N20" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N36="","",'All Direct Jobs'!N36)</x:f>
+      </x:c>
+      <x:c r="O20" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O36="","",'All Direct Jobs'!O36)</x:f>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="13" t="inlineStr">
@@ -10257,13 +10710,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M21" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N21" s="13" t="str"/>
-      <x:c r="O21" s="13" t="str"/>
+      <x:c r="M21" s="13" t="str">
+        <x:f>'All Direct Jobs'!M37</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N21" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N37="","",'All Direct Jobs'!N37)</x:f>
+      </x:c>
+      <x:c r="O21" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O37="","",'All Direct Jobs'!O37)</x:f>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="13" t="inlineStr">
@@ -10326,13 +10782,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M22" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N22" s="13" t="str"/>
-      <x:c r="O22" s="13" t="str"/>
+      <x:c r="M22" s="13" t="str">
+        <x:f>'All Direct Jobs'!M38</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N22" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N38="","",'All Direct Jobs'!N38)</x:f>
+      </x:c>
+      <x:c r="O22" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O38="","",'All Direct Jobs'!O38)</x:f>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="13" t="inlineStr">
@@ -10395,13 +10854,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M23" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N23" s="13" t="str"/>
-      <x:c r="O23" s="13" t="str"/>
+      <x:c r="M23" s="13" t="str">
+        <x:f>'All Direct Jobs'!M39</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N23" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N39="","",'All Direct Jobs'!N39)</x:f>
+      </x:c>
+      <x:c r="O23" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O39="","",'All Direct Jobs'!O39)</x:f>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="13" t="inlineStr">
@@ -10464,13 +10926,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M24" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N24" s="13" t="str"/>
-      <x:c r="O24" s="13" t="str"/>
+      <x:c r="M24" s="13" t="str">
+        <x:f>'All Direct Jobs'!M40</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N24" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N40="","",'All Direct Jobs'!N40)</x:f>
+      </x:c>
+      <x:c r="O24" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O40="","",'All Direct Jobs'!O40)</x:f>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="13" t="inlineStr">
@@ -10533,13 +10998,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M25" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N25" s="13" t="str"/>
-      <x:c r="O25" s="13" t="str"/>
+      <x:c r="M25" s="13" t="str">
+        <x:f>'All Direct Jobs'!M43</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N25" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N43="","",'All Direct Jobs'!N43)</x:f>
+      </x:c>
+      <x:c r="O25" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O43="","",'All Direct Jobs'!O43)</x:f>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="13" t="inlineStr">
@@ -10602,13 +11070,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M26" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N26" s="13" t="str"/>
-      <x:c r="O26" s="13" t="str"/>
+      <x:c r="M26" s="13" t="str">
+        <x:f>'All Direct Jobs'!M43</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N26" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N43="","",'All Direct Jobs'!N43)</x:f>
+      </x:c>
+      <x:c r="O26" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O43="","",'All Direct Jobs'!O43)</x:f>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="13" t="inlineStr">
@@ -10671,13 +11142,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M27" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N27" s="13" t="str"/>
-      <x:c r="O27" s="13" t="str"/>
+      <x:c r="M27" s="13" t="str">
+        <x:f>'All Direct Jobs'!M44</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N27" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N44="","",'All Direct Jobs'!N44)</x:f>
+      </x:c>
+      <x:c r="O27" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O44="","",'All Direct Jobs'!O44)</x:f>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="13" t="inlineStr">
@@ -10740,13 +11214,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M28" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N28" s="13" t="str"/>
-      <x:c r="O28" s="13" t="str"/>
+      <x:c r="M28" s="13" t="str">
+        <x:f>'All Direct Jobs'!M46</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N28" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N46="","",'All Direct Jobs'!N46)</x:f>
+      </x:c>
+      <x:c r="O28" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O46="","",'All Direct Jobs'!O46)</x:f>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="13" t="inlineStr">
@@ -10809,13 +11286,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M29" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N29" s="13" t="str"/>
-      <x:c r="O29" s="13" t="str"/>
+      <x:c r="M29" s="13" t="str">
+        <x:f>'All Direct Jobs'!M47</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N29" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N47="","",'All Direct Jobs'!N47)</x:f>
+      </x:c>
+      <x:c r="O29" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O47="","",'All Direct Jobs'!O47)</x:f>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="13" t="inlineStr">
@@ -10878,13 +11358,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M30" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N30" s="13" t="str"/>
-      <x:c r="O30" s="13" t="str"/>
+      <x:c r="M30" s="13" t="str">
+        <x:f>'All Direct Jobs'!M48</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N30" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N48="","",'All Direct Jobs'!N48)</x:f>
+      </x:c>
+      <x:c r="O30" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O48="","",'All Direct Jobs'!O48)</x:f>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="13" t="inlineStr">
@@ -10947,13 +11430,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M31" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N31" s="13" t="str"/>
-      <x:c r="O31" s="13" t="str"/>
+      <x:c r="M31" s="13" t="str">
+        <x:f>'All Direct Jobs'!M49</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N31" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N49="","",'All Direct Jobs'!N49)</x:f>
+      </x:c>
+      <x:c r="O31" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O49="","",'All Direct Jobs'!O49)</x:f>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="13" t="inlineStr">
@@ -11016,13 +11502,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M32" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N32" s="13" t="str"/>
-      <x:c r="O32" s="13" t="str"/>
+      <x:c r="M32" s="13" t="str">
+        <x:f>'All Direct Jobs'!M50</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N32" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N50="","",'All Direct Jobs'!N50)</x:f>
+      </x:c>
+      <x:c r="O32" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O50="","",'All Direct Jobs'!O50)</x:f>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="13" t="inlineStr">
@@ -11085,13 +11574,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M33" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N33" s="13" t="str"/>
-      <x:c r="O33" s="13" t="str"/>
+      <x:c r="M33" s="13" t="str">
+        <x:f>'All Direct Jobs'!M52</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N33" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N52="","",'All Direct Jobs'!N52)</x:f>
+      </x:c>
+      <x:c r="O33" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O52="","",'All Direct Jobs'!O52)</x:f>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="13" t="inlineStr">
@@ -11154,13 +11646,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M34" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N34" s="13" t="str"/>
-      <x:c r="O34" s="13" t="str"/>
+      <x:c r="M34" s="13" t="str">
+        <x:f>'All Direct Jobs'!M53</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N34" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N53="","",'All Direct Jobs'!N53)</x:f>
+      </x:c>
+      <x:c r="O34" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O53="","",'All Direct Jobs'!O53)</x:f>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="13" t="inlineStr">
@@ -11223,13 +11718,16 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M35" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N35" s="13" t="str"/>
-      <x:c r="O35" s="13" t="str"/>
+      <x:c r="M35" s="13" t="str">
+        <x:f>'All Direct Jobs'!M54</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N35" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N54="","",'All Direct Jobs'!N54)</x:f>
+      </x:c>
+      <x:c r="O35" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O54="","",'All Direct Jobs'!O54)</x:f>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="13" t="inlineStr">
@@ -11292,136 +11790,134 @@
           <x:t xml:space="preserve">2026-10-26</x:t>
         </x:is>
       </x:c>
-      <x:c r="M36" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Applied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N36" s="13" t="str"/>
-      <x:c r="O36" s="13" t="str"/>
+      <x:c r="M36" s="13" t="str">
+        <x:f>'All Direct Jobs'!M55</x:f>
+        <x:v>Not Applied</x:v>
+      </x:c>
+      <x:c r="N36" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!N55="","",'All Direct Jobs'!N55)</x:f>
+      </x:c>
+      <x:c r="O36" s="13" t="str">
+        <x:f>IF('All Direct Jobs'!O55="","",'All Direct Jobs'!O55)</x:f>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="M2:M100">
-    <x:cfRule type="expression" dxfId="27" priority="1">
+    <x:cfRule type="expression" dxfId="53" priority="1">
       <x:formula>M2="Not Applied"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="28" priority="2">
+    <x:cfRule type="expression" dxfId="54" priority="2">
       <x:formula>M2="Planning to Apply"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="29" priority="3">
+    <x:cfRule type="expression" dxfId="55" priority="3">
       <x:formula>M2="Applied"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="30" priority="4">
+    <x:cfRule type="expression" dxfId="56" priority="4">
       <x:formula>M2="Under Consideration"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="31" priority="5">
+    <x:cfRule type="expression" dxfId="57" priority="5">
       <x:formula>M2="OA / Assessment"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="32" priority="6">
+    <x:cfRule type="expression" dxfId="58" priority="6">
       <x:formula>M2="Recruiter Screen"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="33" priority="7">
+    <x:cfRule type="expression" dxfId="59" priority="7">
       <x:formula>M2="Interview"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="34" priority="8">
+    <x:cfRule type="expression" dxfId="60" priority="8">
       <x:formula>M2="Final Round"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="35" priority="9">
+    <x:cfRule type="expression" dxfId="61" priority="9">
       <x:formula>M2="Offer"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="36" priority="10">
+    <x:cfRule type="expression" dxfId="62" priority="10">
       <x:formula>M2="Rejected"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="37" priority="11">
+    <x:cfRule type="expression" dxfId="63" priority="11">
       <x:formula>M2="Withdrawn"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="38" priority="12">
+    <x:cfRule type="expression" dxfId="64" priority="12">
       <x:formula>M2="Not Going to Apply"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="39" priority="13">
+    <x:cfRule type="expression" dxfId="65" priority="13">
       <x:formula>M2="Closed / Expired"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="M2:M100">
-      <x:formula1>"Not Applied,Planning to Apply,Applied,Under Consideration,OA / Assessment,Recruiter Screen,Interview,Final Round,Offer,Rejected,Withdrawn,Not Going to Apply,Closed / Expired"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="R5dfd2884e3054c8e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="Rd826e3f532d54004"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="Ra699ae0212d3409c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="R1911eb7f5d5e4b16"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="R909b5ce770eb48f0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R827f10887b974823"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="R849fe11eb7624ae9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R81ca73891d9c454c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="Rde0e47d312144caa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="Rf5c9c2cac0ee4c96"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="R0a3b93ef89534aa2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R4d6fd31605cb47a1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="Rb7e32e48e77f4b01"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R90227a4a803a4d2a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="R5f0e73bf1d914740"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Ra0d6c591d8e24eed"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R18e06d98cdda4f27"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R027a290d84374a91"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="R41611aab0d4a43fd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="Re2c8e69746d14123"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="Ree02308837bf4e6f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="Rc08296dd9cd84524"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="Rae1550e94e88468d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R178c9a6cb5cb4167"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="R7629cc56adab4ac4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R6ed2c043754845c0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="R1d008c72dad84480"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Ra00538b95b594260"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="R8bed594074f44afd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R62ebb443dd974528"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R97648e32cda24919"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="R521630bf0fdb440b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="R8cf1459dd40e48df"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="R48df356f88014b22"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="Re1ddbc8ee26048b6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Ra6380fa003c340f4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="R1c1631b91aec43fd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R4a44e48272644282"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="Rc58a0a30a0234264"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="R6c708318f3364eb3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="Recfcadbb0c55444d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="R030d3b00511c42f4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="Rb7f287665d2f4c52"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R19fc25ad84704979"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="R7a0213786ae845fe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R970a76c131844bb7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R90fc7f5800a04afd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R0cf1f46c7a19413c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="Rdf9c37236a2243f7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R9c19b32405d1406e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="Rf947aa3f4380449e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="R8229bc9875f24029"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="R87350bb408704030"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Rc0210be48f9e477f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="Rd8ea13b2e7884a80"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="Rb0a5405258734adc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="Refa01a981b3a4691"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="Rff09f985540743c3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="Rcd82a4eaaee54b17"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R9b7fa81392114888"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="Re988d42c846446ef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="Re9139c7643004d34"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="R35cf8309cb8b45c5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="Rd4bae50318214143"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="Rcbf4299e36b247f5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R983fcb59c9c646a2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="Rec1cb6a7c4ea44f5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R4866709e33ba4196"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="R940007995b7a48b1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="R65e300f1795c4a03"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="R2b009a9d2b164280"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="Re77b9bca2cb54afd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="Rbbfb59757e5a41ce"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="R6971c18a7b214986"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="Rd62ec6ac282a45b5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R39a04e9184314c64"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="R93ff55bd26bf409f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R99f1c7d73a524361"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="R01eca86c81a34abc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R676d7f327f9a4a2d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="Rb4d7d30ca2b846d5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R58442b42e637403e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="R05c5a7e39f9d40c5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="Rfcd6b4be464f44be"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="R4c8fda15561b4883"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R6eac45a6a6454141"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="Rdb53dbc69f1c4ec2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Rf168ad3c089740f8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="R97a4b56ea7c4449f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="Rd46efc46f41047bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="R304b3c4818f04e40"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="R3c5dcbfbca694b84"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="R2d5fbcbae2f24328"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rc7f3bfa85a634545"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="R4ce05b258c6c47c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R6c9ab74fa54e4d9c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="R0a1ff8a416674aae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Rf18b6ced484d4dc3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="R1ba5baaef26c4b5e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Rfd58f318ed5944c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R98e069b1361048c7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="Red71a9b5fe4c4c27"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="R49eb0f89e7e24959"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="Rd669b173c16e4d16"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="Rd81958b0e31e4306"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R7b469128c233495c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Rbd408f89d0164535"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R069334cb54b5492d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="Re0bc83c002b34bda"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="Rff6c619329a54680"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="R475ea79ff5914bf1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Re926cedd4ed849e0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="R7d87c542cab64a70"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Rf981e1d14ac14bec"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="R4e20822b95fb4828"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="Rbf2a11debf8f4c73"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="Rf7e956111206484e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="Rfeb867ac71c2448f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="R5be796192a794c24"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R8f78fda8756542d4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="R8755e729230b4859"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="R6cb3beebed0c4bdd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="R7bc23b78b4054f77"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R83dc1273cd0b4f22"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="R1e3a10db10be4f89"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="Rdb9da7e1388e4b3f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="R1d78b4f9595a4b37"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="R67c5cc12ea274082"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="R35dade7b4e5c4ea8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="R742082f421514d29"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="R84e2274091ec40e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="Rdb3076c98f7e408a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="R32626db9beff4447"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="Ra7a49fd0cb0d4cc3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="Re8f4ab5785834500"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R6f3e8673fd79490b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="R02519619ebb14372"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R9f2fa0b01ff448b7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="R2f06a51c57bb473a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Ra1c9ac5449434592"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfacda1f9b2bd46fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07b3dc5cd2f2420e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11739,6 +12235,46 @@
         <x:v>Posting closed before applying or is no longer active.</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="119" t="str">
+        <x:v>Single source of truth</x:v>
+      </x:c>
+      <x:c r="B23" s="119" t="str">
+        <x:v>All Direct Jobs is the only sheet where Status, Date Applied, and Notes should be edited.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="79" t="str">
+        <x:v>Apply First</x:v>
+      </x:c>
+      <x:c r="B24" s="79" t="str">
+        <x:v>Priority view. Status / Date Applied / Notes are formulas linked to All Direct Jobs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="79" t="str">
+        <x:v>Best Resume Matches</x:v>
+      </x:c>
+      <x:c r="B25" s="79" t="str">
+        <x:v>Resume-fit view. Status / Date Applied / Notes are formulas linked to All Direct Jobs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="79" t="str">
+        <x:v>Duplicate jobs</x:v>
+      </x:c>
+      <x:c r="B26" s="79" t="str">
+        <x:v>A job can appear in multiple views, but its application state exists only once in All Direct Jobs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="79" t="str">
+        <x:v>How to update</x:v>
+      </x:c>
+      <x:c r="B27" s="79" t="str">
+        <x:v>Change the dropdown/status in All Direct Jobs. The linked views update automatically when Excel recalculates.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
